--- a/classroom.xlsx
+++ b/classroom.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +613,36 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CS-Year2-Comp1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CS-Year2-Comp2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arts</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/classroom.xlsx
+++ b/classroom.xlsx
@@ -1,34 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A90355-A134-4365-A6C5-D8E864BEFF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+  <si>
+    <t>Classroom ID</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Required Hours/Week</t>
+  </si>
+  <si>
+    <t>CS-Year2-Comp1</t>
+  </si>
+  <si>
+    <t>Data Structures</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Algorithms</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Operating Systems</t>
+  </si>
+  <si>
+    <t>Database Systems</t>
+  </si>
+  <si>
+    <t>Software Engineering</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>CS-Year2-Comp2</t>
+  </si>
+  <si>
+    <t>Art</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Art</t>
+  </si>
+  <si>
+    <t>CS-Year1-Comp1</t>
+  </si>
+  <si>
+    <t>Maths 1</t>
+  </si>
+  <si>
+    <t>Sports</t>
+  </si>
+  <si>
+    <t>CS-Year1-Comp1</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>Engineering Drawing</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thermodynamics</t>
+  </si>
+  <si>
+    <t>CS-Year1-Comp2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +126,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,239 +428,314 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Classroom ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Required Hours/Week</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Data Structures</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Algorithms</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Operating Systems</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Database Systems</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
         <v>5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Software Engineering</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22">
         <v>4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Data Structures</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Algorithms</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Operating Systems</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
         <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Database Systems</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Software Engineering</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Art</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CS-Year2-Comp2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/classroom.xlsx
+++ b/classroom.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A90355-A134-4365-A6C5-D8E864BEFF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="24">
   <si>
     <t>Classroom ID</t>
   </si>
@@ -62,19 +61,20 @@
     <t>2</t>
   </si>
   <si>
-    <t>Art</t>
-  </si>
-  <si>
     <t>CS-Year1-Comp1</t>
   </si>
   <si>
-    <t>Maths 1</t>
+    <r>
+      <t>Mathematics</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
   </si>
   <si>
     <t>Sports</t>
-  </si>
-  <si>
-    <t>CS-Year1-Comp1</t>
   </si>
   <si>
     <t>Physics</t>
@@ -95,14 +95,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -428,9 +428,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="27.77734375" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -438,7 +438,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -460,7 +460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -471,7 +471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -482,7 +482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -504,7 +504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -515,7 +515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -537,7 +537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -548,7 +548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -559,7 +559,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -570,7 +570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -581,7 +581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -592,31 +592,31 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>17</v>
       </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
@@ -625,9 +625,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -636,56 +636,56 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
         <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
         <v>17</v>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
@@ -694,9 +694,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -705,34 +705,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27">
         <v>5</v>
